--- a/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_64961_completo.xlsx
+++ b/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_64961_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3b647912a43c4a10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc5354dfef72b4176"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
       </x:c>
       <x:c s="" t="inlineStr">
         <x:is>
-          <x:t>Dpto: La Libertad / Prov: Gran Chimu / Dist.: Cascas</x:t>
+          <x:t>Dpto: La Libertad / Prov: Gran Chimú / Dist.: Cascas</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0066</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0069</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0066</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0070</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0072</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0044</x:v>
+        <x:v>      0.0066</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0052</x:v>
+        <x:v>      0.0079</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0069</x:v>
+        <x:v>      0.0107</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0088</x:v>
+        <x:v>      0.0138</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0056</x:v>
+        <x:v>      0.0085</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0070</x:v>
+        <x:v>      0.0109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0063</x:v>
+        <x:v>      0.0098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0072</x:v>
+        <x:v>      0.0113</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0079</x:v>
+        <x:v>      0.0125</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0126</x:v>
+        <x:v>      0.0199</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0116</x:v>
+        <x:v>      0.0185</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0142</x:v>
+        <x:v>      0.0224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0107</x:v>
+        <x:v>      0.0168</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0067</x:v>
+        <x:v>      0.0103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,207 +609,207 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      0.0136</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0127</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0216</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0198</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0222</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0305</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0229</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0149</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0134</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0093</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0081</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0083</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      0.0087</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>30/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0081</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0139</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0137</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0125</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0141</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0195</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0146</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0095</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>22/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0086</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>21/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0060</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>20/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0053</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>19/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0054</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>18/07/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0057</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>17/07/2026</x:t>
         </x:is>
       </x:c>
@@ -684,7 +819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0064</x:v>
+        <x:v>      0.0098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0064</x:v>
+        <x:v>      0.0098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0096</x:v>
+        <x:v>      0.0150</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0063</x:v>
+        <x:v>      0.0097</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0060</x:v>
+        <x:v>      0.0092</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0066</x:v>
+        <x:v>      0.0102</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0065</x:v>
+        <x:v>      0.0099</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0064</x:v>
+        <x:v>      0.0098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0078</x:v>
+        <x:v>      0.0123</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0089</x:v>
+        <x:v>      0.0138</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0064</x:v>
+        <x:v>      0.0098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0064</x:v>
+        <x:v>      0.0098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0071</x:v>
+        <x:v>      0.0110</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0064</x:v>
+        <x:v>      0.0098</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0067</x:v>
+        <x:v>      0.0103</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0082</x:v>
+        <x:v>      0.0129</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,132 +1059,132 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      0.0160</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0098</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0103</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0133</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0104</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0105</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0134</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0164</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/06/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      0.0102</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>30/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0064</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>29/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0067</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>28/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0085</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>27/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0068</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>26/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0068</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>25/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0085</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>24/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0105</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>23/06/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.0066</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>22/06/2026</x:t>
         </x:is>
       </x:c>
@@ -1059,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0089</x:v>
+        <x:v>      0.0140</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0129</x:v>
+        <x:v>      0.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0138</x:v>
+        <x:v>      0.0218</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0137</x:v>
+        <x:v>      0.0217</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0146</x:v>
+        <x:v>      0.0230</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0161</x:v>
+        <x:v>      0.0253</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0111</x:v>
+        <x:v>      0.0176</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0111</x:v>
+        <x:v>      0.0176</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0122</x:v>
+        <x:v>      0.0193</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0113</x:v>
+        <x:v>      0.0180</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0116</x:v>
+        <x:v>      0.0184</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0134</x:v>
+        <x:v>      0.0212</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0146</x:v>
+        <x:v>      0.0231</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0119</x:v>
+        <x:v>      0.0189</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0121</x:v>
+        <x:v>      0.0192</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0124</x:v>
+        <x:v>      0.0197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0129</x:v>
+        <x:v>      0.0204</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0133</x:v>
+        <x:v>      0.0211</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0165</x:v>
+        <x:v>      0.0259</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0167</x:v>
+        <x:v>      0.0261</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0128</x:v>
+        <x:v>      0.0203</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0124</x:v>
+        <x:v>      0.0197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0140</x:v>
+        <x:v>      0.0221</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0162</x:v>
+        <x:v>      0.0254</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0169</x:v>
+        <x:v>      0.0265</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0171</x:v>
+        <x:v>      0.0268</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0209</x:v>
+        <x:v>      0.0325</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0173</x:v>
+        <x:v>      0.0272</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0211</x:v>
+        <x:v>      0.0328</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0200</x:v>
+        <x:v>      0.0312</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0189</x:v>
+        <x:v>      0.0296</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0251</x:v>
+        <x:v>      0.0379</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1244</x:v>
+        <x:v>      0.1450</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0858</x:v>
+        <x:v>      0.1094</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.0591</x:v>
+        <x:v>      0.0817</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_64961_completo.xlsx
+++ b/13772_Cuenca_Chicama/_raw_reportes_xlsx/IDConfig_64961_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rc5354dfef72b4176"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R12bca25f1897496e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0052</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0054</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0046</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0072</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0081</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0072</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0065</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0059</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0068</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0050</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0047</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0054</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0047</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0059</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0055</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0074</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0054</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0069</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0062</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0055</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0060</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0090</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0057</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0056</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0064</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0066</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0067</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0103</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0059</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.0057</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
